--- a/punmicro/templates/writing/U18.xlsx
+++ b/punmicro/templates/writing/U18.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="内容编写" sheetId="1" r:id="R60ffabcd72a14be1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图片与视频" sheetId="2" r:id="R19e1c6ee9f6b48df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEO与Schema" sheetId="3" r:id="R8a238b39ea0648ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发检查" sheetId="4" r:id="R30cec35c0e2a4601"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="内容编写" sheetId="1" r:id="R4e8a39f0296c4fb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图片与视频" sheetId="2" r:id="Rfd7e6e0b8299454f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEO与Schema" sheetId="3" r:id="Ra2e32002c0fc4e77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发检查" sheetId="4" r:id="Rbef13c51dd59428c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -649,7 +649,7 @@
         <x:v>特定方法的要求</x:v>
       </x:c>
       <x:c r="E11" s="3" t="str">
-        <x:v>围绕 特定方法的要求 解释这一节问题，补充适用条件、具体例子和可核验来源。</x:v>
+        <x:v>解释厌氧培养方法所需的具体条件，并简要区分微需氧培养和细胞低氧任务；不同方法和版本使用各自的资料。</x:v>
       </x:c>
       <x:c r="F11" s="3" t="str">
         <x:v>Peptostreptococcus anaerobius is discussed through its biological background and cited research, connecting anaerobic microbiology with laboratory equipment needs.
@@ -671,7 +671,7 @@
         <x:v>研究段落较长，主文没有H2/H3问题分组。 把背景、证据范围和实验室任务分开；补观察/环境要求的高层解释，不新增病原培养操作规程。</x:v>
       </x:c>
       <x:c r="N11" s="3" t="str">
-        <x:v>分问题层级、当前文献与具名审阅。</x:v>
+        <x:v>方法来源与专业审阅；对应版本的任务和使用条件。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="149" customHeight="1">
@@ -1032,7 +1032,7 @@
         <x:v>pun-IPAN 资料</x:v>
       </x:c>
       <x:c r="E20" s="3" t="str">
-        <x:v>围绕 pun-IPAN 资料 解释这一节问题，补充适用条件、具体例子和可核验来源。</x:v>
+        <x:v>为厌氧读者提供pun-IPAN厌氧版本资料；若任务属于微需氧或细胞与组织低氧培养，引导到低氧版本的相应说明。</x:v>
       </x:c>
       <x:c r="F20" s="3" t="str">
         <x:v>The stated capacity is 960–1,120 plates of 90 mm, depending on configuration. Capacity needs to be read with loading and option details.
@@ -1058,7 +1058,7 @@
 FAQ区为空状态；容量需在段落中理解布局条件。 加入布局示意及各配置容量/可用操作空间表。</x:v>
       </x:c>
       <x:c r="N20" s="3" t="str">
-        <x:v>pun-IPAN工程数据及已确认的文件。</x:v>
+        <x:v>各版本的真实资料入口、适用范围和文件版本。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -8706,7 +8706,7 @@
         <x:v>Anaerobic Culture: Concepts and Workspace Needs | Punmicro</x:v>
       </x:c>
       <x:c r="D19" s="3" t="str">
-        <x:v>厌氧培养：概念与工作空间需求 | Punmicro</x:v>
+        <x:v>厌氧细菌培养——概念与工作环境需求 | Punmicro</x:v>
       </x:c>
       <x:c r="E19" s="8" t="str"/>
       <x:c r="F19" s="3" t="str">
@@ -8729,9 +8729,7 @@
       <x:c r="C20" s="3" t="str">
         <x:v>Learn how anaerobic culture needs relate to laboratory workspace and handling considerations. Discuss model-specific equipment requirements with Punmicro.</x:v>
       </x:c>
-      <x:c r="D20" s="3" t="str">
-        <x:v>了解厌氧培养需求与实验室工作空间、操作条件之间的关系，并与 Punmicro 沟通具体型号的设备要求。</x:v>
-      </x:c>
+      <x:c r="D20" s="3" t="str"/>
       <x:c r="E20" s="8" t="str"/>
       <x:c r="F20" s="3" t="str">
         <x:v>准确摘要，不固定字符数；搜索引擎可能重新生成片段。</x:v>
@@ -8830,7 +8828,7 @@
         <x:v>Anaerobic Culture: Concepts and Workspace Needs | Punmicro</x:v>
       </x:c>
       <x:c r="D25" s="3" t="str">
-        <x:v>厌氧培养：概念与工作空间需求 | Punmicro</x:v>
+        <x:v>厌氧细菌培养——概念与工作环境需求 | Punmicro</x:v>
       </x:c>
       <x:c r="E25" s="8" t="str"/>
       <x:c r="F25" s="3" t="str">
@@ -8853,9 +8851,7 @@
       <x:c r="C26" s="3" t="str">
         <x:v>Learn how anaerobic culture needs relate to laboratory workspace and handling considerations. Discuss model-specific equipment requirements with Punmicro.</x:v>
       </x:c>
-      <x:c r="D26" s="3" t="str">
-        <x:v>了解厌氧培养需求与实验室工作空间、操作条件之间的关系，并与 Punmicro 沟通具体型号的设备要求。</x:v>
-      </x:c>
+      <x:c r="D26" s="3" t="str"/>
       <x:c r="E26" s="8" t="str"/>
       <x:c r="F26" s="3" t="str">
         <x:v>可编辑，需与内容相符。</x:v>
@@ -8970,7 +8966,7 @@
         <x:v>Anaerobic Culture: Concepts and Workspace Needs | Punmicro</x:v>
       </x:c>
       <x:c r="D32" s="3" t="str">
-        <x:v>厌氧培养：概念与工作空间需求 | Punmicro</x:v>
+        <x:v>厌氧细菌培养——概念与工作环境需求 | Punmicro</x:v>
       </x:c>
       <x:c r="E32" s="8" t="str"/>
       <x:c r="F32" s="3" t="str">
@@ -8993,9 +8989,7 @@
       <x:c r="C33" s="3" t="str">
         <x:v>Learn how anaerobic culture needs relate to laboratory workspace and handling considerations. Discuss model-specific equipment requirements with Punmicro.</x:v>
       </x:c>
-      <x:c r="D33" s="3" t="str">
-        <x:v>了解厌氧培养需求与实验室工作空间、操作条件之间的关系，并与 Punmicro 沟通具体型号的设备要求。</x:v>
-      </x:c>
+      <x:c r="D33" s="3" t="str"/>
       <x:c r="E33" s="8" t="str"/>
       <x:c r="F33" s="3" t="str">
         <x:v>可沿用已审核摘要。</x:v>
@@ -9501,7 +9495,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="164" customHeight="1">
+    <x:row r="64" ht="48" customHeight="1">
       <x:c r="A64" s="3" t="str">
         <x:v>竞品分析</x:v>
       </x:c>
@@ -9573,7 +9567,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" ht="48" customHeight="1">
+    <x:row r="68" ht="74" customHeight="1">
       <x:c r="A68" s="3" t="str">
         <x:v>竞品分析</x:v>
       </x:c>
@@ -9591,7 +9585,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="74" customHeight="1">
+    <x:row r="69" ht="48" customHeight="1">
       <x:c r="A69" s="3" t="str">
         <x:v>竞品分析</x:v>
       </x:c>
@@ -9699,7 +9693,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="48" customHeight="1">
+    <x:row r="75" ht="74" customHeight="1">
       <x:c r="A75" s="3" t="str">
         <x:v>竞品分析</x:v>
       </x:c>
@@ -9717,7 +9711,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="74" customHeight="1">
+    <x:row r="76" ht="48" customHeight="1">
       <x:c r="A76" s="3" t="str">
         <x:v>竞品分析</x:v>
       </x:c>
@@ -9753,7 +9747,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" ht="48" customHeight="1">
+    <x:row r="78" ht="74" customHeight="1">
       <x:c r="A78" s="3" t="str">
         <x:v>竞品分析</x:v>
       </x:c>
@@ -9771,7 +9765,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="74" customHeight="1">
+    <x:row r="79" ht="48" customHeight="1">
       <x:c r="A79" s="3" t="str">
         <x:v>竞品分析</x:v>
       </x:c>
@@ -9847,7 +9841,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="48" customHeight="1">
+    <x:row r="83" ht="59" customHeight="1">
       <x:c r="A83" s="3" t="str">
         <x:v>正文示范</x:v>
       </x:c>
@@ -9867,7 +9861,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="59" customHeight="1">
+    <x:row r="84" ht="48" customHeight="1">
       <x:c r="A84" s="3" t="str">
         <x:v>竞品媒体</x:v>
       </x:c>
@@ -10157,7 +10151,7 @@
         <x:v>https://www.dwscientific.com/blog/anaerobic-workstations-vs-anaerobic-jars</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="134" customHeight="1">
+    <x:row r="99" ht="48" customHeight="1">
       <x:c r="A99" s="3" t="str">
         <x:v>竞品分析</x:v>
       </x:c>
@@ -10211,7 +10205,7 @@
         <x:v>https://www.dwscientific.com/blog/anaerobic-workstations-vs-anaerobic-jars</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="48" customHeight="1">
+    <x:row r="102" ht="59" customHeight="1">
       <x:c r="A102" s="3" t="str">
         <x:v>竞品分析</x:v>
       </x:c>
@@ -10247,7 +10241,7 @@
         <x:v>https://www.dwscientific.com/blog/anaerobic-workstations-vs-anaerobic-jars</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="59" customHeight="1">
+    <x:row r="104" ht="48" customHeight="1">
       <x:c r="A104" s="3" t="str">
         <x:v>竞品分析</x:v>
       </x:c>
@@ -10337,7 +10331,7 @@
         <x:v>https://www.dwscientific.com/blog/anaerobic-workstations-vs-anaerobic-jars</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" ht="48" customHeight="1">
+    <x:row r="109" ht="59" customHeight="1">
       <x:c r="A109" s="3" t="str">
         <x:v>竞品分析</x:v>
       </x:c>
@@ -10373,7 +10367,7 @@
         <x:v>https://www.dwscientific.com/blog/anaerobic-workstations-vs-anaerobic-jars</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" ht="59" customHeight="1">
+    <x:row r="111" ht="48" customHeight="1">
       <x:c r="A111" s="3" t="str">
         <x:v>竞品分析</x:v>
       </x:c>
@@ -10391,7 +10385,7 @@
         <x:v>https://www.dwscientific.com/blog/anaerobic-workstations-vs-anaerobic-jars</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" ht="48" customHeight="1">
+    <x:row r="112" ht="59" customHeight="1">
       <x:c r="A112" s="3" t="str">
         <x:v>竞品分析</x:v>
       </x:c>
@@ -10427,7 +10421,7 @@
         <x:v>https://www.dwscientific.com/blog/anaerobic-workstations-vs-anaerobic-jars</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" ht="59" customHeight="1">
+    <x:row r="114" ht="74" customHeight="1">
       <x:c r="A114" s="3" t="str">
         <x:v>竞品分析</x:v>
       </x:c>
@@ -10466,7 +10460,7 @@
         <x:v>https://www.dwscientific.com/blog/anaerobic-workstations-vs-anaerobic-jars</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" ht="74" customHeight="1">
+    <x:row r="116" ht="59" customHeight="1">
       <x:c r="A116" s="3" t="str">
         <x:v>正文示范</x:v>
       </x:c>
@@ -10486,7 +10480,7 @@
         <x:v>https://www.dwscientific.com/blog/anaerobic-workstations-vs-anaerobic-jars</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" ht="48" customHeight="1">
+    <x:row r="117" ht="59" customHeight="1">
       <x:c r="A117" s="3" t="str">
         <x:v>正文示范</x:v>
       </x:c>
@@ -10506,7 +10500,7 @@
         <x:v>https://www.dwscientific.com/blog/anaerobic-workstations-vs-anaerobic-jars</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" ht="59" customHeight="1">
+    <x:row r="118" ht="48" customHeight="1">
       <x:c r="A118" s="3" t="str">
         <x:v>竞品媒体</x:v>
       </x:c>
@@ -10526,7 +10520,7 @@
         <x:v>https://www.dwscientific.com/blog/anaerobic-workstations-vs-anaerobic-jars</x:v>
       </x:c>
     </x:row>
-    <x:row r="119" ht="59" customHeight="1">
+    <x:row r="119" ht="48" customHeight="1">
       <x:c r="A119" s="3" t="str">
         <x:v>竞品媒体</x:v>
       </x:c>
@@ -10928,7 +10922,7 @@
         <x:v>https://www.dwscientific.com/whitley-anaerobic-workstations</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" ht="48" customHeight="1">
+    <x:row r="141" ht="59" customHeight="1">
       <x:c r="A141" s="3" t="str">
         <x:v>正文示范</x:v>
       </x:c>
@@ -11018,7 +11012,7 @@
         <x:v>https://developers.google.com/search/docs/fundamentals/creating-helpful-content</x:v>
       </x:c>
     </x:row>
-    <x:row r="145" ht="48" customHeight="1">
+    <x:row r="145" ht="179" customHeight="1">
       <x:c r="A145" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11058,7 +11052,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="146">
+    <x:row r="146" ht="179" customHeight="1">
       <x:c r="A146" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11098,7 +11092,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="147">
+    <x:row r="147" ht="179" customHeight="1">
       <x:c r="A147" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11136,7 +11130,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="148">
+    <x:row r="148" ht="179" customHeight="1">
       <x:c r="A148" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11174,7 +11168,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="149">
+    <x:row r="149" ht="179" customHeight="1">
       <x:c r="A149" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11212,7 +11206,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="150">
+    <x:row r="150" ht="179" customHeight="1">
       <x:c r="A150" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11250,7 +11244,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="151">
+    <x:row r="151" ht="179" customHeight="1">
       <x:c r="A151" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11288,7 +11282,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="152">
+    <x:row r="152" ht="179" customHeight="1">
       <x:c r="A152" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11326,7 +11320,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="153">
+    <x:row r="153" ht="179" customHeight="1">
       <x:c r="A153" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11364,7 +11358,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="154">
+    <x:row r="154" ht="179" customHeight="1">
       <x:c r="A154" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11402,7 +11396,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="155">
+    <x:row r="155" ht="179" customHeight="1">
       <x:c r="A155" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11440,7 +11434,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="156">
+    <x:row r="156" ht="179" customHeight="1">
       <x:c r="A156" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11478,7 +11472,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="157">
+    <x:row r="157" ht="179" customHeight="1">
       <x:c r="A157" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11516,7 +11510,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="158">
+    <x:row r="158" ht="179" customHeight="1">
       <x:c r="A158" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11554,7 +11548,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="159">
+    <x:row r="159" ht="179" customHeight="1">
       <x:c r="A159" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11592,7 +11586,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="160">
+    <x:row r="160" ht="179" customHeight="1">
       <x:c r="A160" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11630,7 +11624,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="161">
+    <x:row r="161" ht="179" customHeight="1">
       <x:c r="A161" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11668,7 +11662,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="162">
+    <x:row r="162" ht="179" customHeight="1">
       <x:c r="A162" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11706,7 +11700,7 @@
         <x:v>https://www.dwscientific.com/blog/bacterium-spotlight-peptostreptococcus-anaerobius</x:v>
       </x:c>
     </x:row>
-    <x:row r="163">
+    <x:row r="163" ht="179" customHeight="1">
       <x:c r="A163" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11746,7 +11740,7 @@
         <x:v>https://www.dwscientific.com/blog/anaerobic-workstations-vs-anaerobic-jars</x:v>
       </x:c>
     </x:row>
-    <x:row r="164">
+    <x:row r="164" ht="179" customHeight="1">
       <x:c r="A164" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11786,7 +11780,7 @@
         <x:v>https://www.dwscientific.com/blog/anaerobic-workstations-vs-anaerobic-jars</x:v>
       </x:c>
     </x:row>
-    <x:row r="165">
+    <x:row r="165" ht="179" customHeight="1">
       <x:c r="A165" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11826,7 +11820,7 @@
         <x:v>https://www.dwscientific.com/blog/anaerobic-workstations-vs-anaerobic-jars</x:v>
       </x:c>
     </x:row>
-    <x:row r="166">
+    <x:row r="166" ht="179" customHeight="1">
       <x:c r="A166" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11866,7 +11860,7 @@
         <x:v>https://www.dwscientific.com/blog/anaerobic-workstations-vs-anaerobic-jars</x:v>
       </x:c>
     </x:row>
-    <x:row r="167">
+    <x:row r="167" ht="179" customHeight="1">
       <x:c r="A167" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11906,7 +11900,7 @@
         <x:v>https://www.dwscientific.com/blog/anaerobic-workstations-vs-anaerobic-jars</x:v>
       </x:c>
     </x:row>
-    <x:row r="168">
+    <x:row r="168" ht="179" customHeight="1">
       <x:c r="A168" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11946,7 +11940,7 @@
         <x:v>https://www.dwscientific.com/blog/anaerobic-workstations-vs-anaerobic-jars</x:v>
       </x:c>
     </x:row>
-    <x:row r="169">
+    <x:row r="169" ht="179" customHeight="1">
       <x:c r="A169" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -11984,7 +11978,7 @@
         <x:v>https://www.dwscientific.com/blog/anaerobic-workstations-vs-anaerobic-jars</x:v>
       </x:c>
     </x:row>
-    <x:row r="170">
+    <x:row r="170" ht="179" customHeight="1">
       <x:c r="A170" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -12024,7 +12018,7 @@
         <x:v>https://www.dwscientific.com/whitley-anaerobic-workstations</x:v>
       </x:c>
     </x:row>
-    <x:row r="171">
+    <x:row r="171" ht="179" customHeight="1">
       <x:c r="A171" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
@@ -12064,7 +12058,7 @@
         <x:v>https://www.dwscientific.com/whitley-anaerobic-workstations</x:v>
       </x:c>
     </x:row>
-    <x:row r="172">
+    <x:row r="172" ht="179" customHeight="1">
       <x:c r="A172" s="3" t="str">
         <x:v>关键词机会</x:v>
       </x:c>
